--- a/forms/trg/Formulir_TRG_ais-rg.xlsx
+++ b/forms/trg/Formulir_TRG_ais-rg.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B50)</f>
+        <f>COUNTA(Anggota!B5:B51)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F50)</f>
+        <f>COUNTA(Anggota!F5:F51)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,22 +937,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mediaty, S.E., M.Si., Ak., CA</t>
+          <t>Prof. Dr. Grace Theresia Pontoh, S.E., Ak., M.Si., CA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Public Management Accounting</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Accounting Information System</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -974,17 +974,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Istiyansyah Ulman Idris, M.Sc</t>
+          <t>Prof. Dr. Mediaty, S.E., M.Si., Ak., CA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting</t>
+          <t>Public Management Accounting</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Haniek Khoirunnissa Baja, M.Sc</t>
+          <t>Muhammad Istiyansyah Ulman Idris, M.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Audrey Michelle Wenny Yolanda, M.Acc</t>
+          <t>Haniek Khoirunnissa Baja, M.Sc</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Financial Accounting and Sustainability Accounting</t>
+          <t>Financial Accounting</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1070,11 +1070,7 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4929-5706</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,12 +1085,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Asharin Juwita Purisamya, M.Sc</t>
+          <t>Audrey Michelle Wenny Yolanda, M.Acc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1111,7 +1107,11 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4929-5706</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1126,20 +1126,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Kartini S.E., M.Si., Ak, CA., CRP., CRA</t>
+          <t>Asharin Juwita Purisamya, M.Sc</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
+          <t>Financial Accounting and Sustainability Accounting</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1159,12 +1163,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Irdam Ferdiansah, S.E., Akt., M.Acc., Ph.D</t>
+          <t>Prof. Dr. Kartini S.E., M.Si., Ak, CA., CRP., CRA</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1192,17 +1196,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Navidreza Ahadi, Ph.D, FHEA</t>
+          <t>Muhammad Irdam Ferdiansah, S.E., Akt., M.Acc., Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>University of Derby, United Kingdom</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1225,17 +1229,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Prof. Johnny Jermias, PhD, CA</t>
+          <t>Navidreza Ahadi, Ph.D, FHEA</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Beedie School of Business, Simon Fraser University, Canada</t>
+          <t>University of Derby, United Kingdom</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1258,17 +1262,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Faisal Abdullah, PhD</t>
+          <t>Prof. Johnny Jermias, PhD, CA</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Adelaide University, Australia</t>
+          <t>Beedie School of Business, Simon Fraser University, Canada</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1291,17 +1295,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Sulistya Rusgianto, S.E., MIF., Ph.D</t>
+          <t>Faisal Abdullah, PhD</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Universitas Airlangga, Indonesia</t>
+          <t>Adelaide University, Australia</t>
         </is>
       </c>
       <c r="E15" s="11" t="n"/>
@@ -1324,17 +1328,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Darrell Imanuel Sampetoding</t>
+          <t>Sulistya Rusgianto, S.E., MIF., Ph.D</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Airlangga, Indonesia</t>
         </is>
       </c>
       <c r="E16" s="11" t="n"/>
@@ -1357,12 +1361,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Joe Happines</t>
+          <t>Darrell Imanuel Sampetoding</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1390,12 +1394,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Agnes Ratu</t>
+          <t>Joe Happines</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1423,12 +1427,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Thomasine Lesly</t>
+          <t>Agnes Ratu</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1456,12 +1460,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Wise Lande</t>
+          <t>Thomasine Lesly</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1489,12 +1493,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Siti Maryam M. Sillehu</t>
+          <t>Wise Lande</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1522,12 +1526,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Allfina Mudasir</t>
+          <t>Siti Maryam M. Sillehu</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1555,12 +1559,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Andi Aschayani Siradja</t>
+          <t>Allfina Mudasir</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1588,12 +1592,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Yansen Pratama Kohar</t>
+          <t>Andi Aschayani Siradja</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1621,12 +1625,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Vierly Ananta Upa</t>
+          <t>Yansen Pratama Kohar</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1654,12 +1658,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Arfandi</t>
+          <t>Vierly Ananta Upa</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1687,12 +1691,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Nisma Ariskha Masdar</t>
+          <t>Arfandi</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1720,12 +1724,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Mashud</t>
+          <t>Nisma Ariskha Masdar</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -1753,12 +1757,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Idrawahyuni</t>
+          <t>Mashud</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -1786,12 +1790,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Arga Bhayangkara Handayanto</t>
+          <t>Idrawahyuni</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1819,12 +1823,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>Arga Bhayangkara Handayanto</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -1852,12 +1856,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Charles Tandilino</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -1885,12 +1889,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Maximilian Anting Kalolu</t>
+          <t>Charles Tandilino</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -1918,12 +1922,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Rifka Dwi Edi</t>
+          <t>Maximilian Anting Kalolu</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -1951,12 +1955,12 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Triana Chatarinne Parabak</t>
+          <t>Rifka Dwi Edi</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -1984,12 +1988,12 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Chrisielin Widyana Susanto</t>
+          <t>Triana Chatarinne Parabak</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -2017,12 +2021,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Pricylia Angelina Husein</t>
+          <t>Chrisielin Widyana Susanto</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2050,12 +2054,12 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Anastasia Ruth Wuysan</t>
+          <t>Pricylia Angelina Husein</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2081,10 +2085,26 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="11" t="n"/>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Anastasia Ruth Wuysan</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>AIS-RG is a research group dedicated to advancing Accounting Information Systems through innovative, interdisciplinary, and technology-driven studies. The group focuses on digital accounting, ERP implementation, AIS literacy, and professional adaptation to technological change. By fostering impactful research, strategic collaborations, and policy contributions, AIS-RG supports sustainable development, digital financial inclusion, and public sector transformation in the Society 5.0 era.</t>
+        </is>
+      </c>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="12" t="n"/>
       <c r="H39" s="12" t="n"/>
@@ -2092,7 +2112,11 @@
       <c r="J39" s="12" t="n"/>
       <c r="K39" s="12" t="n"/>
       <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2281,15 +2305,32 @@
       <c r="L50" s="12" t="n"/>
       <c r="M50" s="12" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="12" t="n"/>
+      <c r="M51" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
